--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.45694622780383</v>
+        <v>5.599253762018123</v>
       </c>
       <c r="D2" t="n">
-        <v>32.2667020257028</v>
+        <v>5.243339079176705</v>
       </c>
       <c r="E2" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F2" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.30263461241666</v>
+        <v>4.599178124517707</v>
       </c>
       <c r="D3" t="n">
-        <v>25.75385640433788</v>
+        <v>4.185001665704906</v>
       </c>
       <c r="E3" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F3" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.23561631168889</v>
+        <v>7.350787650649444</v>
       </c>
       <c r="D4" t="n">
-        <v>42.303308202943</v>
+        <v>6.874287582978238</v>
       </c>
       <c r="E4" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F4" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.89406278619785</v>
+        <v>1.77028520275715</v>
       </c>
       <c r="D5" t="n">
-        <v>11.95547769777594</v>
+        <v>1.942765125888591</v>
       </c>
       <c r="E5" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F5" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.96970958053115</v>
+        <v>2.920077806836312</v>
       </c>
       <c r="D6" t="n">
-        <v>20.38025538089144</v>
+        <v>3.311791499394859</v>
       </c>
       <c r="E6" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F6" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.89431108635849</v>
+        <v>7.945325551533255</v>
       </c>
       <c r="D7" t="n">
-        <v>27.52954102783682</v>
+        <v>4.473550417023483</v>
       </c>
       <c r="E7" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F7" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.88544069492268</v>
+        <v>7.131384112924936</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14282236604281</v>
+        <v>6.685708634481958</v>
       </c>
       <c r="E8" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F8" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.338986747639981</v>
+        <v>1.030085346491497</v>
       </c>
       <c r="D9" t="n">
-        <v>9.276440705714197</v>
+        <v>1.507421614678557</v>
       </c>
       <c r="E9" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F9" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>52.13909688981153</v>
+        <v>8.472603244594374</v>
       </c>
       <c r="D10" t="n">
-        <v>49.4889379868721</v>
+        <v>8.041952422866716</v>
       </c>
       <c r="E10" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F10" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.09000557751209</v>
+        <v>5.539625906345714</v>
       </c>
       <c r="D11" t="n">
-        <v>15.36187963178062</v>
+        <v>2.496305440164351</v>
       </c>
       <c r="E11" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F11" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>50.72452860624174</v>
+        <v>8.242735898514283</v>
       </c>
       <c r="D12" t="n">
-        <v>47.75398027286729</v>
+        <v>7.760021794340934</v>
       </c>
       <c r="E12" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F12" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.17683817489095</v>
+        <v>5.06623620341978</v>
       </c>
       <c r="D13" t="n">
-        <v>20.29039585823248</v>
+        <v>3.297189326962777</v>
       </c>
       <c r="E13" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F13" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.76209488662861</v>
+        <v>6.298840419077149</v>
       </c>
       <c r="D14" t="n">
-        <v>33.34815792796072</v>
+        <v>5.419075663293618</v>
       </c>
       <c r="E14" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F14" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.48260267491141</v>
+        <v>3.815922934673104</v>
       </c>
       <c r="D15" t="n">
-        <v>9.830659795685319</v>
+        <v>1.597482216798864</v>
       </c>
       <c r="E15" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F15" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>51.57839012548383</v>
+        <v>8.381488395391122</v>
       </c>
       <c r="D16" t="n">
-        <v>40.45177215980233</v>
+        <v>6.573412975967879</v>
       </c>
       <c r="E16" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F16" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8.049031899163875</v>
+        <v>1.30796768361413</v>
       </c>
       <c r="D17" t="n">
-        <v>29.38431614797058</v>
+        <v>4.774951374045219</v>
       </c>
       <c r="E17" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F17" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>50.7402288865504</v>
+        <v>8.24528719406444</v>
       </c>
       <c r="D18" t="n">
-        <v>34.45150541875911</v>
+        <v>5.598369630548356</v>
       </c>
       <c r="E18" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F18" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>8.276472678623424</v>
+        <v>1.344926810276307</v>
       </c>
       <c r="D19" t="n">
-        <v>13.26810063012282</v>
+        <v>2.156066352394958</v>
       </c>
       <c r="E19" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F19" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>19.69096813048222</v>
+        <v>3.199782321203361</v>
       </c>
       <c r="D20" t="n">
-        <v>8.34105076909459</v>
+        <v>1.355420749977871</v>
       </c>
       <c r="E20" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F20" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>23.50531854708632</v>
+        <v>3.819614263901527</v>
       </c>
       <c r="D21" t="n">
-        <v>22.49115421983916</v>
+        <v>3.654812560723864</v>
       </c>
       <c r="E21" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F21" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>15.5279917426086</v>
+        <v>2.523298658173898</v>
       </c>
       <c r="D22" t="n">
-        <v>15.10217274812071</v>
+        <v>2.454103071569616</v>
       </c>
       <c r="E22" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F22" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>11.88079954294849</v>
+        <v>1.93062992572913</v>
       </c>
       <c r="D23" t="n">
-        <v>12.13676998279704</v>
+        <v>1.97222512220452</v>
       </c>
       <c r="E23" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F23" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>3.619183656417984</v>
+        <v>0.5881173441679224</v>
       </c>
       <c r="D24" t="n">
-        <v>3.841422916285139</v>
+        <v>0.6242312238963352</v>
       </c>
       <c r="E24" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F24" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>11.83816182940131</v>
+        <v>1.923701297277713</v>
       </c>
       <c r="D25" t="n">
-        <v>11.80188141100309</v>
+        <v>1.917805729288002</v>
       </c>
       <c r="E25" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F25" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>23.09800278369838</v>
+        <v>3.753425452350987</v>
       </c>
       <c r="D26" t="n">
-        <v>23.4885413823802</v>
+        <v>3.816887974636783</v>
       </c>
       <c r="E26" t="n">
-        <v>16.01965232774833</v>
+        <v>2.603193503259103</v>
       </c>
       <c r="F26" t="n">
-        <v>12.99996437011709</v>
+        <v>2.112494210144027</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
